--- a/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
+++ b/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
@@ -510,7 +510,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -518,7 +517,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -561,7 +559,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -3252,13 +3249,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Auto-generated · commit df5d2ea · 2026-08-04 14:15 UTC</t>
+          <t>Auto-generated · commit 5c1deff · 2026-08-04 16:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3629,6 +3626,265 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>Force wss:// and https:// for voice transport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Secret scanning in CI (gitleaks)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A.8.8, A.8.4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CC7.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>.github/workflows/security-scan.yml</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Keep gitleaks in CI; enable GitHub push protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAST in CI (CodeQL)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A.8.25, A.8.28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CC8.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>.github/workflows/security-scan.yml</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Keep CodeQL; triage findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dependency/SCA scanning (Dependabot + npm audit)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A.8.8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CC7.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>.github/dependabot.yml</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Keep Dependabot; act on advisories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mandatory code-owner review</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A.8.4, A.8.32</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CC8.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CODEOWNERS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Enable 'Require Code Owner review' in branch protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vulnerability disclosure policy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A.5.5, A.5.24</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CC2.3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SECURITY.md</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Keep current; staff the security mailbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PR governance (security/compliance checklist)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A.8.32</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CC8.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>.github/pull_request_template.md</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Keep; enforce checklist in review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IP / licensing clarity</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A.5.32</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CC1.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>LICENSE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Keep proprietary notice current.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
+++ b/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -510,6 +510,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -517,6 +518,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -559,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -570,6 +573,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>and flags the six documents for review when monitored source files change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Document ownership — Product Owner: Sridhar Muppidi | Product Head: Sachin Tulla | Technical &amp; Security Head: Sachin Tulla</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
+++ b/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
@@ -576,10 +576,11 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Document ownership — Product Owner: Sridhar Muppidi | Product Head: Sachin Tulla | Technical &amp; Security Head: Sachin Tulla</t>
+          <t>Document ownership — Product Owner: Sridhar Muppidi | Product Head: Sachin Tulla | Technical Head: Sachin Tulla | Head of Engineering: Hari PS | Security Head: Anil M</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
+++ b/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
@@ -580,7 +580,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Document ownership — Product Owner: Sridhar Muppidi | Product Head: Sachin Tulla | Technical Head: Sachin Tulla | Head of Engineering: Hari PS | Security Head: Anil M</t>
+          <t>Document ownership — Product Owner: Sridhar Muppidi | Product / Technical Head: Sachin Tulla | Head of Engineering: Hari PS | Security Head: Anil M</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
+++ b/docs/compliance/06-Compliance-Evidence-Pack-and-Claims-Matrix.xlsx
@@ -510,7 +510,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -518,7 +517,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -561,7 +559,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -576,7 +573,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -3266,7 +3262,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Auto-generated · commit 5c1deff · 2026-08-04 16:44 UTC</t>
+          <t>Auto-generated · commit 8126271 · 2026-08-04 18:00 UTC</t>
         </is>
       </c>
     </row>
